--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="47">
   <si>
     <t>No.</t>
   </si>
@@ -35,25 +35,43 @@
     <t>평균</t>
   </si>
   <si>
+    <t>484.3</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
     <t>446.2</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>522.3</t>
+  </si>
+  <si>
+    <t>968.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>03일</t>
   </si>
   <si>
     <t>04일</t>
@@ -445,16 +463,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s" s="31">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s" s="32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -462,19 +480,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -482,19 +500,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -502,19 +520,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -522,19 +540,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -542,19 +560,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -562,19 +580,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -582,19 +600,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -602,19 +620,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -622,19 +640,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -642,19 +660,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -662,19 +680,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -682,19 +700,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -702,19 +720,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -722,19 +740,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -742,19 +760,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -762,19 +780,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -782,19 +800,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -802,19 +820,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -822,19 +840,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -842,19 +860,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -862,19 +880,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -882,19 +900,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -902,19 +920,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -922,19 +940,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -942,19 +960,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -962,19 +980,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -982,19 +1000,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1002,19 +1020,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1022,19 +1040,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="50">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>484.3</t>
+    <t>474.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -71,10 +71,19 @@
     <t>03일</t>
   </si>
   <si>
+    <t>454.6</t>
+  </si>
+  <si>
+    <t>1423.1</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>04일</t>
   </si>
   <si>
     <t>05일</t>
@@ -506,13 +515,13 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -520,19 +529,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -540,19 +549,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -560,19 +569,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -580,19 +589,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -600,19 +609,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -620,19 +629,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -640,19 +649,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -660,19 +669,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -680,19 +689,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -700,19 +709,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -720,19 +729,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -740,19 +749,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -760,19 +769,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -780,19 +789,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -800,19 +809,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -820,19 +829,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -840,19 +849,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -860,19 +869,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -880,19 +889,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -900,19 +909,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -920,19 +929,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -940,19 +949,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -960,19 +969,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -980,19 +989,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1000,19 +1009,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1020,19 +1029,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1040,19 +1049,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="54">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>474.4</t>
+    <t>443.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.4</t>
   </si>
   <si>
     <t>01일</t>
@@ -83,10 +83,22 @@
     <t>04일</t>
   </si>
   <si>
+    <t>349.2</t>
+  </si>
+  <si>
+    <t>1772.3</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>05일</t>
   </si>
   <si>
     <t>06일</t>
@@ -535,13 +547,13 @@
         <v>23</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -549,19 +561,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -569,19 +581,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -589,19 +601,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -609,19 +621,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -629,19 +641,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -649,19 +661,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -669,19 +681,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -689,19 +701,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -709,19 +721,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -729,19 +741,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -749,19 +761,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -769,19 +781,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -789,19 +801,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -809,19 +821,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -829,19 +841,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -849,19 +861,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -869,19 +881,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -889,19 +901,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -909,19 +921,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -929,19 +941,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -949,19 +961,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -969,19 +981,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -989,19 +1001,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1009,19 +1021,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1029,19 +1041,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1049,19 +1061,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="57">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>443.1</t>
+    <t>452.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>4.5</t>
   </si>
   <si>
     <t>01일</t>
@@ -50,9 +50,6 @@
     <t>446.2</t>
   </si>
   <si>
-    <t>4.5</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -98,10 +95,22 @@
     <t>05일</t>
   </si>
   <si>
+    <t>491.6</t>
+  </si>
+  <si>
+    <t>2263.9</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>06일</t>
   </si>
   <si>
     <t>07일</t>
@@ -490,10 +499,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -501,19 +510,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s" s="36">
         <v>13</v>
       </c>
-      <c r="C4" t="s" s="36">
+      <c r="D4" t="s" s="37">
         <v>14</v>
       </c>
-      <c r="D4" t="s" s="37">
+      <c r="E4" t="s" s="38">
         <v>15</v>
       </c>
-      <c r="E4" t="s" s="38">
+      <c r="F4" t="s" s="39">
         <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -521,19 +530,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s" s="31">
         <v>18</v>
       </c>
-      <c r="C5" t="s" s="31">
+      <c r="D5" t="s" s="32">
         <v>19</v>
       </c>
-      <c r="D5" t="s" s="32">
+      <c r="E5" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="34">
         <v>20</v>
-      </c>
-      <c r="E5" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>21</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -541,19 +550,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>22</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>23</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>24</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>25</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -561,19 +570,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>27</v>
-      </c>
-      <c r="C7" t="s" s="31">
-        <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
         <v>28</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -581,19 +590,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -601,19 +610,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -621,19 +630,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -641,19 +650,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -661,19 +670,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -681,19 +690,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -701,19 +710,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -721,19 +730,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -741,19 +750,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -761,19 +770,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -781,19 +790,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -801,19 +810,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -821,19 +830,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -841,19 +850,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -861,19 +870,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -881,19 +890,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -901,19 +910,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -921,19 +930,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -941,19 +950,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -961,19 +970,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -981,19 +990,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1001,19 +1010,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1021,19 +1030,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1041,19 +1050,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1061,19 +1070,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="62">
   <si>
     <t>No.</t>
   </si>
@@ -35,21 +35,24 @@
     <t>평균</t>
   </si>
   <si>
-    <t>452.8</t>
+    <t>468.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>446.2</t>
+  </si>
+  <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>446.2</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -110,10 +113,22 @@
     <t>06일</t>
   </si>
   <si>
+    <t>546.5</t>
+  </si>
+  <si>
+    <t>2810.4</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>07일</t>
   </si>
   <si>
     <t>08일</t>
@@ -499,10 +514,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -510,19 +525,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -530,19 +545,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -550,19 +565,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -570,19 +585,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -590,19 +605,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -610,19 +625,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -630,19 +645,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -650,19 +665,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -670,19 +685,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -690,19 +705,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -710,19 +725,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -730,19 +745,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -750,19 +765,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -770,19 +785,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -790,19 +805,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -810,19 +825,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -830,19 +845,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -850,19 +865,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -870,19 +885,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -890,19 +905,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -910,19 +925,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -930,19 +945,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -950,19 +965,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -970,19 +985,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -990,19 +1005,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1010,19 +1025,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1030,19 +1045,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1050,19 +1065,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1070,19 +1085,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="74">
   <si>
     <t>No.</t>
   </si>
@@ -35,109 +35,145 @@
     <t>평균</t>
   </si>
   <si>
-    <t>468.4</t>
+    <t>437.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>446.2</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>522.3</t>
+  </si>
+  <si>
+    <t>968.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>454.6</t>
+  </si>
+  <si>
+    <t>1423.1</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>349.2</t>
+  </si>
+  <si>
+    <t>1772.3</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>491.6</t>
+  </si>
+  <si>
+    <t>2263.9</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>546.7</t>
+  </si>
+  <si>
+    <t>2810.6</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>269.1</t>
+  </si>
+  <si>
+    <t>3079.7</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>394.6</t>
+  </si>
+  <si>
+    <t>3474.3</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>34.7</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>466.3</t>
+  </si>
+  <si>
+    <t>3940.6</t>
+  </si>
+  <si>
     <t>4.7</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>446.2</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>522.3</t>
-  </si>
-  <si>
-    <t>968.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>454.6</t>
-  </si>
-  <si>
-    <t>1423.1</t>
-  </si>
-  <si>
-    <t>14.2</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>349.2</t>
-  </si>
-  <si>
-    <t>1772.3</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>17.7</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>491.6</t>
-  </si>
-  <si>
-    <t>2263.9</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>22.6</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>546.5</t>
-  </si>
-  <si>
-    <t>2810.4</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>07일</t>
+    <t>39.4</t>
+  </si>
+  <si>
+    <t>10일</t>
   </si>
   <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>10일</t>
   </si>
   <si>
     <t>11일</t>
@@ -631,13 +667,13 @@
         <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -645,19 +681,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -665,19 +701,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -685,19 +721,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -705,19 +741,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -725,19 +761,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -745,19 +781,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -765,19 +801,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -785,19 +821,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -805,19 +841,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -825,19 +861,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -845,19 +881,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -865,19 +901,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -885,19 +921,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -905,19 +941,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -925,19 +961,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -945,19 +981,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -965,19 +1001,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -985,19 +1021,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1005,19 +1041,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1025,19 +1061,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1045,19 +1081,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1065,19 +1101,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1085,19 +1121,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>437.8</t>
+    <t>402.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>4.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -173,13 +173,37 @@
     <t>10일</t>
   </si>
   <si>
+    <t>461.7</t>
+  </si>
+  <si>
+    <t>4402.3</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>44.0</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>21.4</t>
+  </si>
+  <si>
+    <t>4423.7</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>44.2</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>12일</t>
   </si>
   <si>
     <t>13일</t>
@@ -727,13 +751,13 @@
         <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -741,19 +765,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -761,19 +785,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -781,19 +805,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -801,19 +825,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -821,19 +845,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -841,19 +865,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -861,19 +885,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -881,19 +905,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -901,19 +925,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -921,19 +945,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -941,19 +965,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -961,19 +985,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -981,19 +1005,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1001,19 +1025,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1021,19 +1045,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1041,19 +1065,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1061,19 +1085,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1081,19 +1105,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1101,19 +1125,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1121,19 +1145,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="81">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>402.2</t>
+    <t>441.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.0</t>
+    <t>4.4</t>
   </si>
   <si>
     <t>01일</t>
@@ -188,16 +188,13 @@
     <t>11일</t>
   </si>
   <si>
-    <t>21.4</t>
-  </si>
-  <si>
-    <t>4423.7</t>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>44.2</t>
+    <t>455.7</t>
+  </si>
+  <si>
+    <t>4858.0</t>
+  </si>
+  <si>
+    <t>48.6</t>
   </si>
   <si>
     <t>12일</t>
@@ -774,10 +771,10 @@
         <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s" s="34">
         <v>60</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -785,19 +782,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -805,19 +802,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -825,19 +822,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -845,19 +842,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -865,19 +862,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -885,19 +882,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -905,19 +902,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -925,19 +922,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -945,19 +942,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -965,19 +962,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -985,19 +982,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1005,19 +1002,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1025,19 +1022,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1045,19 +1042,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1065,19 +1062,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1085,19 +1082,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1105,19 +1102,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1125,19 +1122,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1145,19 +1142,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>441.6</t>
+    <t>444.3</t>
   </si>
   <si>
     <t>-</t>
@@ -188,13 +188,13 @@
     <t>11일</t>
   </si>
   <si>
-    <t>455.7</t>
-  </si>
-  <si>
-    <t>4858.0</t>
-  </si>
-  <si>
-    <t>48.6</t>
+    <t>485.3</t>
+  </si>
+  <si>
+    <t>4887.6</t>
+  </si>
+  <si>
+    <t>48.9</t>
   </si>
   <si>
     <t>12일</t>
@@ -771,7 +771,7 @@
         <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>60</v>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="84">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>444.3</t>
+    <t>453.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>4.5</t>
   </si>
   <si>
     <t>01일</t>
@@ -50,9 +50,6 @@
     <t>446.2</t>
   </si>
   <si>
-    <t>4.5</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -98,10 +95,10 @@
     <t>05일</t>
   </si>
   <si>
-    <t>491.6</t>
-  </si>
-  <si>
-    <t>2263.9</t>
+    <t>491.7</t>
+  </si>
+  <si>
+    <t>2264.0</t>
   </si>
   <si>
     <t>4.9</t>
@@ -116,7 +113,7 @@
     <t>546.7</t>
   </si>
   <si>
-    <t>2810.6</t>
+    <t>2810.7</t>
   </si>
   <si>
     <t>5.5</t>
@@ -131,7 +128,7 @@
     <t>269.1</t>
   </si>
   <si>
-    <t>3079.7</t>
+    <t>3079.8</t>
   </si>
   <si>
     <t>2.7</t>
@@ -146,7 +143,7 @@
     <t>394.6</t>
   </si>
   <si>
-    <t>3474.3</t>
+    <t>3474.4</t>
   </si>
   <si>
     <t>3.9</t>
@@ -161,7 +158,7 @@
     <t>466.3</t>
   </si>
   <si>
-    <t>3940.6</t>
+    <t>3940.7</t>
   </si>
   <si>
     <t>4.7</t>
@@ -176,7 +173,7 @@
     <t>461.7</t>
   </si>
   <si>
-    <t>4402.3</t>
+    <t>4402.4</t>
   </si>
   <si>
     <t>4.6</t>
@@ -191,7 +188,7 @@
     <t>485.3</t>
   </si>
   <si>
-    <t>4887.6</t>
+    <t>4887.7</t>
   </si>
   <si>
     <t>48.9</t>
@@ -200,10 +197,22 @@
     <t>12일</t>
   </si>
   <si>
+    <t>558.2</t>
+  </si>
+  <si>
+    <t>5445.9</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>54.5</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>13일</t>
   </si>
   <si>
     <t>14일</t>
@@ -571,10 +580,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -582,19 +591,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s" s="36">
         <v>13</v>
       </c>
-      <c r="C4" t="s" s="36">
+      <c r="D4" t="s" s="37">
         <v>14</v>
       </c>
-      <c r="D4" t="s" s="37">
+      <c r="E4" t="s" s="38">
         <v>15</v>
       </c>
-      <c r="E4" t="s" s="38">
+      <c r="F4" t="s" s="39">
         <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -602,19 +611,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s" s="31">
         <v>18</v>
       </c>
-      <c r="C5" t="s" s="31">
+      <c r="D5" t="s" s="32">
         <v>19</v>
       </c>
-      <c r="D5" t="s" s="32">
+      <c r="E5" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="34">
         <v>20</v>
-      </c>
-      <c r="E5" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>21</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -622,19 +631,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>22</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>23</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>24</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>25</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -642,19 +651,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>27</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>28</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>29</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>30</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -662,19 +671,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>32</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>33</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>34</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>35</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -682,19 +691,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>37</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>38</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>39</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>40</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>41</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -702,19 +711,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>42</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>43</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="E10" t="s" s="38">
         <v>44</v>
       </c>
-      <c r="E10" t="s" s="38">
+      <c r="F10" t="s" s="39">
         <v>45</v>
-      </c>
-      <c r="F10" t="s" s="39">
-        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -722,19 +731,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s" s="31">
         <v>47</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="D11" t="s" s="32">
         <v>48</v>
       </c>
-      <c r="D11" t="s" s="32">
+      <c r="E11" t="s" s="33">
         <v>49</v>
       </c>
-      <c r="E11" t="s" s="33">
+      <c r="F11" t="s" s="34">
         <v>50</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -742,19 +751,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>52</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>53</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>54</v>
       </c>
-      <c r="E12" t="s" s="38">
+      <c r="F12" t="s" s="39">
         <v>55</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -762,19 +771,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s" s="34">
         <v>59</v>
-      </c>
-      <c r="E13" t="s" s="33">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>60</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -782,19 +791,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>61</v>
-      </c>
-      <c r="C14" t="s" s="36">
-        <v>62</v>
       </c>
       <c r="D14" t="s" s="37">
         <v>62</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -802,19 +811,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -822,19 +831,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -842,19 +851,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -862,19 +871,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -882,19 +891,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -902,19 +911,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -922,19 +931,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -942,19 +951,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -962,19 +971,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -982,19 +991,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1002,19 +1011,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1022,19 +1031,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1042,19 +1051,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1062,19 +1071,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1082,19 +1091,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1102,19 +1111,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1122,19 +1131,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1142,19 +1151,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
   <si>
     <t>No.</t>
   </si>
@@ -35,21 +35,24 @@
     <t>평균</t>
   </si>
   <si>
-    <t>453.8</t>
+    <t>463.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>446.2</t>
+  </si>
+  <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>446.2</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -176,9 +179,6 @@
     <t>4402.4</t>
   </si>
   <si>
-    <t>4.6</t>
-  </si>
-  <si>
     <t>44.0</t>
   </si>
   <si>
@@ -212,10 +212,22 @@
     <t>13일</t>
   </si>
   <si>
+    <t>573.2</t>
+  </si>
+  <si>
+    <t>6019.1</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>60.2</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>14일</t>
   </si>
   <si>
     <t>15일</t>
@@ -580,10 +592,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -591,19 +603,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -611,19 +623,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -631,19 +643,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -651,19 +663,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -671,19 +683,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -691,19 +703,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -711,19 +723,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -731,19 +743,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -751,16 +763,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s" s="39">
         <v>55</v>
@@ -780,7 +792,7 @@
         <v>58</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>59</v>
@@ -817,13 +829,13 @@
         <v>66</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -831,19 +843,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -851,19 +863,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -871,19 +883,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -891,19 +903,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -911,19 +923,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -931,19 +943,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -951,19 +963,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -971,19 +983,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -991,19 +1003,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1011,19 +1023,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1031,19 +1043,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1051,19 +1063,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1071,19 +1083,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1091,19 +1103,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1111,19 +1123,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1131,19 +1143,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1151,19 +1163,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>463.0</t>
+    <t>464.0</t>
   </si>
   <si>
     <t>-</t>
@@ -227,10 +227,22 @@
     <t>14일</t>
   </si>
   <si>
+    <t>476.6</t>
+  </si>
+  <si>
+    <t>6495.7</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>65.0</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>15일</t>
   </si>
   <si>
     <t>16일</t>
@@ -849,13 +861,13 @@
         <v>71</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -863,19 +875,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -883,19 +895,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -903,19 +915,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -923,19 +935,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -943,19 +955,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -963,19 +975,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -983,19 +995,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1003,19 +1015,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1023,19 +1035,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1043,19 +1055,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1063,19 +1075,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1083,19 +1095,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1103,19 +1115,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1123,19 +1135,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1143,19 +1155,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1163,19 +1175,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="95">
   <si>
     <t>No.</t>
   </si>
@@ -35,150 +35,150 @@
     <t>평균</t>
   </si>
   <si>
-    <t>464.0</t>
+    <t>470.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>446.2</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>522.3</t>
+  </si>
+  <si>
+    <t>968.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>454.6</t>
+  </si>
+  <si>
+    <t>1423.1</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>349.2</t>
+  </si>
+  <si>
+    <t>1772.3</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>491.7</t>
+  </si>
+  <si>
+    <t>2264.0</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>546.7</t>
+  </si>
+  <si>
+    <t>2810.7</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>269.1</t>
+  </si>
+  <si>
+    <t>3079.8</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>394.6</t>
+  </si>
+  <si>
+    <t>3474.4</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>34.7</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>466.3</t>
+  </si>
+  <si>
+    <t>3940.7</t>
+  </si>
+  <si>
+    <t>39.4</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>461.7</t>
+  </si>
+  <si>
+    <t>4402.4</t>
+  </si>
+  <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>446.2</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>522.3</t>
-  </si>
-  <si>
-    <t>968.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>454.6</t>
-  </si>
-  <si>
-    <t>1423.1</t>
-  </si>
-  <si>
-    <t>14.2</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>349.2</t>
-  </si>
-  <si>
-    <t>1772.3</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>17.7</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>491.7</t>
-  </si>
-  <si>
-    <t>2264.0</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>22.6</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>546.7</t>
-  </si>
-  <si>
-    <t>2810.7</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>269.1</t>
-  </si>
-  <si>
-    <t>3079.8</t>
-  </si>
-  <si>
-    <t>2.7</t>
-  </si>
-  <si>
-    <t>30.8</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>394.6</t>
-  </si>
-  <si>
-    <t>3474.4</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>34.7</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>466.3</t>
-  </si>
-  <si>
-    <t>3940.7</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>39.4</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>461.7</t>
-  </si>
-  <si>
-    <t>4402.4</t>
-  </si>
-  <si>
     <t>44.0</t>
   </si>
   <si>
@@ -242,10 +242,19 @@
     <t>15일</t>
   </si>
   <si>
+    <t>565.0</t>
+  </si>
+  <si>
+    <t>7060.7</t>
+  </si>
+  <si>
+    <t>70.6</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>16일</t>
   </si>
   <si>
     <t>17일</t>
@@ -764,10 +773,10 @@
         <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s" s="34">
         <v>50</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -775,16 +784,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>52</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>53</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>54</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>9</v>
       </c>
       <c r="F12" t="s" s="39">
         <v>55</v>
@@ -881,13 +890,13 @@
         <v>76</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -895,19 +904,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -915,19 +924,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -935,19 +944,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -955,19 +964,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -975,19 +984,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -995,19 +1004,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1015,19 +1024,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1035,19 +1044,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1055,19 +1064,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1075,19 +1084,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1095,19 +1104,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1115,19 +1124,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1135,19 +1144,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1155,19 +1164,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1175,19 +1184,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="98">
   <si>
     <t>No.</t>
   </si>
@@ -35,135 +35,138 @@
     <t>평균</t>
   </si>
   <si>
-    <t>470.7</t>
+    <t>476.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>446.2</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>522.3</t>
+  </si>
+  <si>
+    <t>968.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>454.6</t>
+  </si>
+  <si>
+    <t>1423.1</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>349.2</t>
+  </si>
+  <si>
+    <t>1772.3</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>491.7</t>
+  </si>
+  <si>
+    <t>2264.0</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>546.7</t>
+  </si>
+  <si>
+    <t>2810.7</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>269.1</t>
+  </si>
+  <si>
+    <t>3079.8</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>394.6</t>
+  </si>
+  <si>
+    <t>3474.4</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>34.7</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>466.3</t>
+  </si>
+  <si>
+    <t>3940.7</t>
+  </si>
+  <si>
     <t>4.7</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>446.2</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>522.3</t>
-  </si>
-  <si>
-    <t>968.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>454.6</t>
-  </si>
-  <si>
-    <t>1423.1</t>
-  </si>
-  <si>
-    <t>14.2</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>349.2</t>
-  </si>
-  <si>
-    <t>1772.3</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>17.7</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>491.7</t>
-  </si>
-  <si>
-    <t>2264.0</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>22.6</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>546.7</t>
-  </si>
-  <si>
-    <t>2810.7</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>269.1</t>
-  </si>
-  <si>
-    <t>3079.8</t>
-  </si>
-  <si>
-    <t>2.7</t>
-  </si>
-  <si>
-    <t>30.8</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>394.6</t>
-  </si>
-  <si>
-    <t>3474.4</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>34.7</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>466.3</t>
-  </si>
-  <si>
-    <t>3940.7</t>
-  </si>
-  <si>
     <t>39.4</t>
   </si>
   <si>
@@ -233,9 +236,6 @@
     <t>6495.7</t>
   </si>
   <si>
-    <t>4.8</t>
-  </si>
-  <si>
     <t>65.0</t>
   </si>
   <si>
@@ -254,10 +254,19 @@
     <t>16일</t>
   </si>
   <si>
+    <t>567.5</t>
+  </si>
+  <si>
+    <t>7628.2</t>
+  </si>
+  <si>
+    <t>76.3</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>17일</t>
   </si>
   <si>
     <t>18일</t>
@@ -773,10 +782,10 @@
         <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -784,19 +793,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -804,19 +813,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
         <v>30</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -824,19 +833,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -844,19 +853,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -864,16 +873,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s" s="39">
         <v>74</v>
@@ -893,7 +902,7 @@
         <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s" s="34">
         <v>78</v>
@@ -910,13 +919,13 @@
         <v>80</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -924,19 +933,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -944,19 +953,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -964,19 +973,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -984,19 +993,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1004,19 +1013,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1024,19 +1033,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1044,19 +1053,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1064,19 +1073,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1084,19 +1093,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1104,19 +1113,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1124,19 +1133,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1144,19 +1153,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1164,19 +1173,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1184,19 +1193,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="102">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>476.8</t>
+    <t>478.2</t>
   </si>
   <si>
     <t>-</t>
@@ -266,10 +266,22 @@
     <t>17일</t>
   </si>
   <si>
+    <t>500.4</t>
+  </si>
+  <si>
+    <t>8128.6</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>81.3</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>18일</t>
   </si>
   <si>
     <t>19일</t>
@@ -939,13 +951,13 @@
         <v>84</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -953,19 +965,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -973,19 +985,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -993,19 +1005,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1013,19 +1025,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1033,19 +1045,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1053,19 +1065,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1073,19 +1085,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1093,19 +1105,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1113,19 +1125,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1133,19 +1145,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1153,19 +1165,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1173,19 +1185,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1193,19 +1205,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="105">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>478.2</t>
+    <t>482.8</t>
   </si>
   <si>
     <t>-</t>
@@ -281,10 +281,19 @@
     <t>18일</t>
   </si>
   <si>
+    <t>562.0</t>
+  </si>
+  <si>
+    <t>8690.6</t>
+  </si>
+  <si>
+    <t>86.9</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>19일</t>
   </si>
   <si>
     <t>20일</t>
@@ -971,13 +980,13 @@
         <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -985,19 +994,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1005,19 +1014,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1025,19 +1034,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1045,19 +1054,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1065,19 +1074,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1085,19 +1094,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1105,19 +1114,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1125,19 +1134,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1145,19 +1154,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1165,19 +1174,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1185,19 +1194,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1205,19 +1214,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="109">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>482.8</t>
+    <t>478.7</t>
   </si>
   <si>
     <t>-</t>
@@ -293,10 +293,22 @@
     <t>19일</t>
   </si>
   <si>
+    <t>403.9</t>
+  </si>
+  <si>
+    <t>9094.5</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>90.9</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>20일</t>
   </si>
   <si>
     <t>21일</t>
@@ -1000,13 +1012,13 @@
         <v>93</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1014,19 +1026,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1034,19 +1046,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1054,19 +1066,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1074,19 +1086,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1094,19 +1106,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1114,19 +1126,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1134,19 +1146,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1154,19 +1166,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1174,19 +1186,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1194,19 +1206,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1214,19 +1226,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="113">
   <si>
     <t>No.</t>
   </si>
@@ -35,207 +35,207 @@
     <t>평균</t>
   </si>
   <si>
-    <t>478.7</t>
+    <t>460.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>446.2</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>522.3</t>
+  </si>
+  <si>
+    <t>968.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>454.6</t>
+  </si>
+  <si>
+    <t>1423.1</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>349.2</t>
+  </si>
+  <si>
+    <t>1772.3</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>491.7</t>
+  </si>
+  <si>
+    <t>2264.0</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>546.7</t>
+  </si>
+  <si>
+    <t>2810.7</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>269.1</t>
+  </si>
+  <si>
+    <t>3079.8</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>394.6</t>
+  </si>
+  <si>
+    <t>3474.4</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>34.7</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>466.3</t>
+  </si>
+  <si>
+    <t>3940.7</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>39.4</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>461.7</t>
+  </si>
+  <si>
+    <t>4402.4</t>
+  </si>
+  <si>
+    <t>44.0</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>485.3</t>
+  </si>
+  <si>
+    <t>4887.7</t>
+  </si>
+  <si>
+    <t>48.9</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>558.2</t>
+  </si>
+  <si>
+    <t>5445.9</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>54.5</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
+    <t>573.2</t>
+  </si>
+  <si>
+    <t>6019.1</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>60.2</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
+    <t>476.6</t>
+  </si>
+  <si>
+    <t>6495.7</t>
+  </si>
+  <si>
     <t>4.8</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>446.2</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>522.3</t>
-  </si>
-  <si>
-    <t>968.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>454.6</t>
-  </si>
-  <si>
-    <t>1423.1</t>
-  </si>
-  <si>
-    <t>14.2</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>349.2</t>
-  </si>
-  <si>
-    <t>1772.3</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>17.7</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>491.7</t>
-  </si>
-  <si>
-    <t>2264.0</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>22.6</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>546.7</t>
-  </si>
-  <si>
-    <t>2810.7</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>269.1</t>
-  </si>
-  <si>
-    <t>3079.8</t>
-  </si>
-  <si>
-    <t>2.7</t>
-  </si>
-  <si>
-    <t>30.8</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>394.6</t>
-  </si>
-  <si>
-    <t>3474.4</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>34.7</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>466.3</t>
-  </si>
-  <si>
-    <t>3940.7</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>39.4</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>461.7</t>
-  </si>
-  <si>
-    <t>4402.4</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>44.0</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>485.3</t>
-  </si>
-  <si>
-    <t>4887.7</t>
-  </si>
-  <si>
-    <t>48.9</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>558.2</t>
-  </si>
-  <si>
-    <t>5445.9</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>54.5</t>
-  </si>
-  <si>
-    <t>13일</t>
-  </si>
-  <si>
-    <t>573.2</t>
-  </si>
-  <si>
-    <t>6019.1</t>
-  </si>
-  <si>
-    <t>5.7</t>
-  </si>
-  <si>
-    <t>60.2</t>
-  </si>
-  <si>
-    <t>14일</t>
-  </si>
-  <si>
-    <t>476.6</t>
-  </si>
-  <si>
-    <t>6495.7</t>
-  </si>
-  <si>
     <t>65.0</t>
   </si>
   <si>
@@ -308,10 +308,22 @@
     <t>20일</t>
   </si>
   <si>
+    <t>114.6</t>
+  </si>
+  <si>
+    <t>9209.1</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>92.1</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>21일</t>
   </si>
   <si>
     <t>22일</t>
@@ -835,10 +847,10 @@
         <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s" s="39">
         <v>55</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -846,19 +858,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
-      </c>
-      <c r="D13" t="s" s="32">
-        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
         <v>30</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -866,19 +878,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>61</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>62</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>63</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>64</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>65</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -886,19 +898,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>66</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>67</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>68</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>69</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -906,16 +918,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>71</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>72</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>73</v>
-      </c>
-      <c r="E16" t="s" s="38">
-        <v>9</v>
       </c>
       <c r="F16" t="s" s="39">
         <v>74</v>
@@ -935,7 +947,7 @@
         <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s" s="34">
         <v>78</v>
@@ -955,7 +967,7 @@
         <v>81</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s" s="39">
         <v>82</v>
@@ -995,7 +1007,7 @@
         <v>90</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s" s="39">
         <v>91</v>
@@ -1032,13 +1044,13 @@
         <v>98</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1046,19 +1058,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1066,19 +1078,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1086,19 +1098,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1106,19 +1118,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1126,19 +1138,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1146,19 +1158,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1166,19 +1178,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1186,19 +1198,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1206,19 +1218,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1226,19 +1238,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>460.5</t>
+    <t>456.1</t>
   </si>
   <si>
     <t>-</t>
@@ -323,10 +323,22 @@
     <t>21일</t>
   </si>
   <si>
+    <t>368.0</t>
+  </si>
+  <si>
+    <t>9577.1</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>95.8</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>22일</t>
   </si>
   <si>
     <t>23일</t>
@@ -1064,13 +1076,13 @@
         <v>103</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1078,19 +1090,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1098,19 +1110,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1118,19 +1130,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1138,19 +1150,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1158,19 +1170,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1178,19 +1190,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1198,19 +1210,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1218,19 +1230,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1238,19 +1250,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="124">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>456.1</t>
+    <t>458.4</t>
   </si>
   <si>
     <t>-</t>
@@ -338,13 +338,34 @@
     <t>22일</t>
   </si>
   <si>
+    <t>372.9</t>
+  </si>
+  <si>
+    <t>9950.0</t>
+  </si>
+  <si>
+    <t>99.5</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
+    <t>592.5</t>
+  </si>
+  <si>
+    <t>10542.5</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>105.4</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>23일</t>
-  </si>
-  <si>
-    <t>24일</t>
   </si>
   <si>
     <t>25일</t>
@@ -1096,13 +1117,13 @@
         <v>108</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1110,19 +1131,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1130,19 +1151,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1150,19 +1171,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1170,19 +1191,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1190,19 +1211,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1210,19 +1231,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1230,19 +1251,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1250,19 +1271,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="127">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>458.4</t>
+    <t>459.5</t>
   </si>
   <si>
     <t>-</t>
@@ -365,10 +365,19 @@
     <t>24일</t>
   </si>
   <si>
+    <t>485.6</t>
+  </si>
+  <si>
+    <t>11028.1</t>
+  </si>
+  <si>
+    <t>110.3</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>25일</t>
   </si>
   <si>
     <t>26일</t>
@@ -1157,13 +1166,13 @@
         <v>117</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1171,19 +1180,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1191,19 +1200,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1211,19 +1220,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1231,19 +1240,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1251,19 +1260,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1271,19 +1280,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="131">
   <si>
     <t>No.</t>
   </si>
@@ -35,150 +35,150 @@
     <t>평균</t>
   </si>
   <si>
-    <t>459.5</t>
+    <t>452.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>446.2</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>522.3</t>
+  </si>
+  <si>
+    <t>968.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>454.6</t>
+  </si>
+  <si>
+    <t>1423.1</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>349.2</t>
+  </si>
+  <si>
+    <t>1772.3</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>491.7</t>
+  </si>
+  <si>
+    <t>2264.0</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>546.7</t>
+  </si>
+  <si>
+    <t>2810.7</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>269.1</t>
+  </si>
+  <si>
+    <t>3079.8</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>394.6</t>
+  </si>
+  <si>
+    <t>3474.4</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>34.7</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>466.3</t>
+  </si>
+  <si>
+    <t>3940.7</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>39.4</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>461.7</t>
+  </si>
+  <si>
+    <t>4402.4</t>
+  </si>
+  <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>446.2</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>522.3</t>
-  </si>
-  <si>
-    <t>968.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>454.6</t>
-  </si>
-  <si>
-    <t>1423.1</t>
-  </si>
-  <si>
-    <t>14.2</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>349.2</t>
-  </si>
-  <si>
-    <t>1772.3</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>17.7</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>491.7</t>
-  </si>
-  <si>
-    <t>2264.0</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>22.6</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>546.7</t>
-  </si>
-  <si>
-    <t>2810.7</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>269.1</t>
-  </si>
-  <si>
-    <t>3079.8</t>
-  </si>
-  <si>
-    <t>2.7</t>
-  </si>
-  <si>
-    <t>30.8</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>394.6</t>
-  </si>
-  <si>
-    <t>3474.4</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>34.7</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>466.3</t>
-  </si>
-  <si>
-    <t>3940.7</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>39.4</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>461.7</t>
-  </si>
-  <si>
-    <t>4402.4</t>
-  </si>
-  <si>
     <t>44.0</t>
   </si>
   <si>
@@ -377,10 +377,22 @@
     <t>25일</t>
   </si>
   <si>
+    <t>286.2</t>
+  </si>
+  <si>
+    <t>11314.3</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>113.1</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>26일</t>
   </si>
   <si>
     <t>27일</t>
@@ -709,10 +721,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -720,19 +732,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s" s="36">
         <v>13</v>
       </c>
-      <c r="C4" t="s" s="36">
+      <c r="D4" t="s" s="37">
         <v>14</v>
       </c>
-      <c r="D4" t="s" s="37">
+      <c r="E4" t="s" s="38">
         <v>15</v>
       </c>
-      <c r="E4" t="s" s="38">
+      <c r="F4" t="s" s="39">
         <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -740,19 +752,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s" s="31">
         <v>18</v>
       </c>
-      <c r="C5" t="s" s="31">
+      <c r="D5" t="s" s="32">
         <v>19</v>
       </c>
-      <c r="D5" t="s" s="32">
+      <c r="E5" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="34">
         <v>20</v>
-      </c>
-      <c r="E5" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>21</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -760,19 +772,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>22</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>23</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>24</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>25</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -780,19 +792,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>27</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>28</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>29</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>30</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -800,19 +812,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>32</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>33</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>34</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>35</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -820,19 +832,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>37</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>38</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>39</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>40</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>41</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -840,19 +852,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>42</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>43</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="E10" t="s" s="38">
         <v>44</v>
       </c>
-      <c r="E10" t="s" s="38">
+      <c r="F10" t="s" s="39">
         <v>45</v>
-      </c>
-      <c r="F10" t="s" s="39">
-        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -860,19 +872,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s" s="31">
         <v>47</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="D11" t="s" s="32">
         <v>48</v>
       </c>
-      <c r="D11" t="s" s="32">
+      <c r="E11" t="s" s="33">
         <v>49</v>
       </c>
-      <c r="E11" t="s" s="33">
+      <c r="F11" t="s" s="34">
         <v>50</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -880,16 +892,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>52</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>53</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>54</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>9</v>
       </c>
       <c r="F12" t="s" s="39">
         <v>55</v>
@@ -909,7 +921,7 @@
         <v>58</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>59</v>
@@ -1169,7 +1181,7 @@
         <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s" s="39">
         <v>119</v>
@@ -1186,13 +1198,13 @@
         <v>121</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1200,19 +1212,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1220,19 +1232,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1240,19 +1252,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1260,19 +1272,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1280,19 +1292,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="133">
   <si>
     <t>No.</t>
   </si>
@@ -35,21 +35,24 @@
     <t>평균</t>
   </si>
   <si>
-    <t>452.6</t>
+    <t>456.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>446.2</t>
+  </si>
+  <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>446.2</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -176,9 +179,6 @@
     <t>4402.4</t>
   </si>
   <si>
-    <t>4.6</t>
-  </si>
-  <si>
     <t>44.0</t>
   </si>
   <si>
@@ -392,10 +392,16 @@
     <t>26일</t>
   </si>
   <si>
+    <t>11872.5</t>
+  </si>
+  <si>
+    <t>118.7</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>27일</t>
   </si>
   <si>
     <t>28일</t>
@@ -721,10 +727,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -732,19 +738,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -752,19 +758,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -772,19 +778,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -792,19 +798,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -812,19 +818,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -832,19 +838,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -852,19 +858,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -872,19 +878,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -892,16 +898,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s" s="39">
         <v>55</v>
@@ -921,7 +927,7 @@
         <v>58</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>59</v>
@@ -1181,7 +1187,7 @@
         <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s" s="39">
         <v>119</v>
@@ -1215,16 +1221,16 @@
         <v>125</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s" s="37">
         <v>126</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1232,19 +1238,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1252,19 +1258,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1272,19 +1278,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1292,19 +1298,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="137">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>456.6</t>
+    <t>455.5</t>
   </si>
   <si>
     <t>-</t>
@@ -401,10 +401,22 @@
     <t>27일</t>
   </si>
   <si>
+    <t>424.9</t>
+  </si>
+  <si>
+    <t>12297.4</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>123.0</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>28일</t>
   </si>
   <si>
     <t>29일</t>
@@ -1244,13 +1256,13 @@
         <v>129</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1258,19 +1270,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1278,19 +1290,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1298,19 +1310,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="140">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>455.5</t>
+    <t>459.1</t>
   </si>
   <si>
     <t>-</t>
@@ -416,10 +416,19 @@
     <t>28일</t>
   </si>
   <si>
+    <t>558.5</t>
+  </si>
+  <si>
+    <t>12855.9</t>
+  </si>
+  <si>
+    <t>128.6</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>29일</t>
   </si>
   <si>
     <t>30일</t>
@@ -1276,13 +1285,13 @@
         <v>134</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1290,19 +1299,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1310,19 +1319,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="144">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>459.1</t>
+    <t>461.9</t>
   </si>
   <si>
     <t>-</t>
@@ -416,10 +416,10 @@
     <t>28일</t>
   </si>
   <si>
-    <t>558.5</t>
-  </si>
-  <si>
-    <t>12855.9</t>
+    <t>558.6</t>
+  </si>
+  <si>
+    <t>12856.0</t>
   </si>
   <si>
     <t>128.6</t>
@@ -428,10 +428,22 @@
     <t>29일</t>
   </si>
   <si>
+    <t>538.5</t>
+  </si>
+  <si>
+    <t>13394.5</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>133.9</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>30일</t>
   </si>
 </sst>
 </file>
@@ -1305,13 +1317,13 @@
         <v>138</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1319,19 +1331,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-06-01.xlsx
+++ b/past_data/site_8024/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="146">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>461.9</t>
+    <t>462.6</t>
   </si>
   <si>
     <t>-</t>
@@ -443,7 +443,13 @@
     <t>30일</t>
   </si>
   <si>
-    <t>0.0</t>
+    <t>484.9</t>
+  </si>
+  <si>
+    <t>13879.4</t>
+  </si>
+  <si>
+    <t>138.8</t>
   </si>
 </sst>
 </file>
@@ -1337,13 +1343,13 @@
         <v>143</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
